--- a/data.mn/public/datasets/mongolbank-deposit-rate-fx-monthly.xlsx
+++ b/data.mn/public/datasets/mongolbank-deposit-rate-fx-monthly.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B197"/>
+  <dimension ref="A1:B199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2391,6 +2391,26 @@
       </c>
       <c r="B197" t="n">
         <v>4.13</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>4.11</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B197"/>
+  <dimension ref="A1:B199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4383,6 +4403,26 @@
         <v>4.13</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
